--- a/test.xlsx
+++ b/test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studenthcmusedu-my.sharepoint.com/personal/23127379_student_hcmus_edu_vn/Documents/University/Nam 2/6th/PPT/Do an 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF982073-70CB-4064-9178-FF57831A429D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{AF982073-70CB-4064-9178-FF57831A429D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E59BB6D7-E1F3-4DC8-9246-8B3305BAAD65}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" xr2:uid="{39E4412B-D21D-415E-A3F4-54808DEF0C90}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{39E4412B-D21D-415E-A3F4-54808DEF0C90}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,6 +130,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
